--- a/web/Pipistrelli 2025.xlsx
+++ b/web/Pipistrelli 2025.xlsx
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.51224563052615</v>
+        <v>45.59746520960268</v>
       </c>
       <c r="I2" t="n">
-        <v>11.51682731007314</v>
+        <v>11.54687495840081</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>45.57578501254513</v>
+        <v>45.50665671632508</v>
       </c>
       <c r="I3" t="n">
-        <v>11.52940362904924</v>
+        <v>11.59015463679549</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45.56270807179739</v>
+        <v>45.53089578038835</v>
       </c>
       <c r="I4" t="n">
-        <v>11.52582275710794</v>
+        <v>11.50945956132898</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45.55240767419862</v>
+        <v>45.54048701756293</v>
       </c>
       <c r="I5" t="n">
-        <v>11.50860331187142</v>
+        <v>11.57704819816247</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.55698486292027</v>
+        <v>45.56546313417498</v>
       </c>
       <c r="I6" t="n">
-        <v>11.49653359519287</v>
+        <v>11.54539076489067</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45.51644088167304</v>
+        <v>45.5188596165759</v>
       </c>
       <c r="I7" t="n">
-        <v>11.59457933505053</v>
+        <v>11.57135076220658</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>45.56189848527787</v>
+        <v>45.58150146270299</v>
       </c>
       <c r="I8" t="n">
-        <v>11.51441900767388</v>
+        <v>11.54978839303273</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>45.51233787631135</v>
+        <v>45.55409738399385</v>
       </c>
       <c r="I9" t="n">
-        <v>11.54781161720944</v>
+        <v>11.5057750812334</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>45.48237227003097</v>
+        <v>45.39859105204894</v>
       </c>
       <c r="I10" t="n">
-        <v>12.3510073318516</v>
+        <v>12.3532020872167</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>45.49988130303833</v>
+        <v>45.56413567836782</v>
       </c>
       <c r="I11" t="n">
-        <v>11.58477401937173</v>
+        <v>11.54698172176243</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>45.53289686563217</v>
+        <v>45.51198118170051</v>
       </c>
       <c r="I13" t="n">
-        <v>11.51315562136176</v>
+        <v>11.54937540075043</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>45.54355139644313</v>
+        <v>45.5712410503055</v>
       </c>
       <c r="I14" t="n">
-        <v>11.5748616928763</v>
+        <v>11.54255823653188</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>45.45399449674756</v>
+        <v>45.37054234805176</v>
       </c>
       <c r="I15" t="n">
-        <v>11.85780444104728</v>
+        <v>11.90185411920182</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>45.56722754626792</v>
+        <v>45.59540516567597</v>
       </c>
       <c r="I16" t="n">
-        <v>11.50350135068841</v>
+        <v>11.56170727553564</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45.5091133148545</v>
+        <v>45.53682668259852</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5114046886542</v>
+        <v>11.50620100671729</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.55006260423264</v>
+        <v>45.57998327883453</v>
       </c>
       <c r="I18" t="n">
-        <v>11.56143077825308</v>
+        <v>11.5798464453228</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45.56739862666263</v>
+        <v>45.5239010030983</v>
       </c>
       <c r="I19" t="n">
-        <v>11.53422259063848</v>
+        <v>11.52598429530358</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>45.58368875226346</v>
+        <v>45.51536076925926</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5897006193112</v>
+        <v>11.5097741402916</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>45.4992019516155</v>
+        <v>45.52569963861534</v>
       </c>
       <c r="I21" t="n">
-        <v>11.56502251341304</v>
+        <v>11.55317328625458</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>45.5203780650403</v>
+        <v>45.51926084994588</v>
       </c>
       <c r="I22" t="n">
-        <v>11.55468914016341</v>
+        <v>11.59228741471364</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>45.5629970040122</v>
+        <v>45.54889467449403</v>
       </c>
       <c r="I23" t="n">
-        <v>11.50176416748012</v>
+        <v>11.53136438565799</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>45.37565081168027</v>
+        <v>45.3617966835512</v>
       </c>
       <c r="I24" t="n">
-        <v>11.92158021243172</v>
+        <v>11.92244842967261</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45.5112631020366</v>
+        <v>45.56976462330759</v>
       </c>
       <c r="I25" t="n">
-        <v>11.5604395361968</v>
+        <v>11.52305838545647</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>45.52722380899727</v>
+        <v>45.58787122665229</v>
       </c>
       <c r="I26" t="n">
-        <v>11.5256481244345</v>
+        <v>11.56635051870573</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>45.39536439560444</v>
+        <v>45.39667096162415</v>
       </c>
       <c r="I27" t="n">
-        <v>11.92560910706797</v>
+        <v>11.91159743996491</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>45.6506773541478</v>
+        <v>45.63465244819743</v>
       </c>
       <c r="I28" t="n">
-        <v>12.20815863693793</v>
+        <v>12.27304707059356</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>45.43697015300241</v>
+        <v>45.45591464714174</v>
       </c>
       <c r="I29" t="n">
-        <v>12.34965626699808</v>
+        <v>12.27581224369264</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>45.55978557728125</v>
+        <v>45.53288489399203</v>
       </c>
       <c r="I31" t="n">
-        <v>11.58911930941772</v>
+        <v>11.52509956452623</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>45.54049055869347</v>
+        <v>45.53804902292848</v>
       </c>
       <c r="I33" t="n">
-        <v>11.54630076610908</v>
+        <v>11.51630340235046</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45.41859279838316</v>
+        <v>45.36721287265154</v>
       </c>
       <c r="I34" t="n">
-        <v>11.84262129831087</v>
+        <v>11.84375631967432</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>45.36414552842256</v>
+        <v>45.41516307424141</v>
       </c>
       <c r="I35" t="n">
-        <v>11.82956387760531</v>
+        <v>11.87425044468943</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>45.40608871408072</v>
+        <v>45.39394350365104</v>
       </c>
       <c r="I36" t="n">
-        <v>11.88952892725061</v>
+        <v>11.86264944974869</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>45.53607288372619</v>
+        <v>45.54888413735789</v>
       </c>
       <c r="I37" t="n">
-        <v>11.57887460631207</v>
+        <v>11.58651501284913</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>45.56675602440758</v>
+        <v>45.53992413212389</v>
       </c>
       <c r="I38" t="n">
-        <v>11.56207091570033</v>
+        <v>11.50277486485785</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>45.59259551188337</v>
+        <v>45.58182328369017</v>
       </c>
       <c r="I39" t="n">
-        <v>11.50648755842639</v>
+        <v>11.52371195226056</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>45.52549056558861</v>
+        <v>45.54467157883811</v>
       </c>
       <c r="I40" t="n">
-        <v>11.55073625164832</v>
+        <v>11.51709928205664</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>45.54999560224778</v>
+        <v>45.51508258367015</v>
       </c>
       <c r="I41" t="n">
-        <v>11.52607603032732</v>
+        <v>11.52575753088252</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>45.42738656672403</v>
+        <v>45.38936975985517</v>
       </c>
       <c r="I42" t="n">
-        <v>11.92212913640072</v>
+        <v>11.89441625817105</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>45.54472756154334</v>
+        <v>45.59669172085987</v>
       </c>
       <c r="I44" t="n">
-        <v>11.50224112056848</v>
+        <v>11.49650043121449</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>45.51306187305985</v>
+        <v>45.54414052677295</v>
       </c>
       <c r="I45" t="n">
-        <v>11.49866315422734</v>
+        <v>11.58004515545104</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45.44706583388685</v>
+        <v>45.39075596863377</v>
       </c>
       <c r="I46" t="n">
-        <v>11.92177205052427</v>
+        <v>11.84149615700036</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>45.55374409760736</v>
+        <v>45.52041274911857</v>
       </c>
       <c r="I47" t="n">
-        <v>11.56125200535716</v>
+        <v>11.53536848969485</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>45.59415023095327</v>
+        <v>45.58575099037269</v>
       </c>
       <c r="I48" t="n">
-        <v>11.57082428055518</v>
+        <v>11.57257266055018</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>45.57190364409229</v>
+        <v>45.52665888208475</v>
       </c>
       <c r="I49" t="n">
-        <v>11.53953119119503</v>
+        <v>11.50648397312396</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45.38204275320828</v>
+        <v>45.38579987747783</v>
       </c>
       <c r="I50" t="n">
-        <v>11.9263332346271</v>
+        <v>11.84016514249408</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>45.53873867665136</v>
+        <v>45.51790769672546</v>
       </c>
       <c r="I51" t="n">
-        <v>11.57257869840013</v>
+        <v>11.51525540342129</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>45.58449808101984</v>
+        <v>45.52814238856895</v>
       </c>
       <c r="I52" t="n">
-        <v>11.52932129594191</v>
+        <v>11.49737834123315</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45.58207730317365</v>
+        <v>45.51307898108984</v>
       </c>
       <c r="I53" t="n">
-        <v>11.5629299099667</v>
+        <v>11.53098413860831</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>45.56564553575238</v>
+        <v>45.52329375183771</v>
       </c>
       <c r="I54" t="n">
-        <v>11.53966615373968</v>
+        <v>11.54589144793436</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>45.58296013074744</v>
+        <v>45.50433431452348</v>
       </c>
       <c r="I55" t="n">
-        <v>11.51981625566114</v>
+        <v>11.5631631145361</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>45.52849644480763</v>
+        <v>45.59114292707615</v>
       </c>
       <c r="I56" t="n">
-        <v>11.54309992098475</v>
+        <v>11.5026718458598</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>45.50778473090293</v>
+        <v>45.54256338559654</v>
       </c>
       <c r="I57" t="n">
-        <v>11.51438884169889</v>
+        <v>11.55839856127538</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>45.42435980829306</v>
+        <v>45.43105016742511</v>
       </c>
       <c r="I58" t="n">
-        <v>12.35403481726495</v>
+        <v>12.32583382319703</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>45.5144985832986</v>
+        <v>45.56519491648769</v>
       </c>
       <c r="I59" t="n">
-        <v>11.5572214190754</v>
+        <v>11.57917755774779</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>45.39019048050879</v>
+        <v>45.42952990740333</v>
       </c>
       <c r="I60" t="n">
-        <v>11.92169277480979</v>
+        <v>11.91123509694358</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>45.47226274110828</v>
+        <v>45.40308870504211</v>
       </c>
       <c r="I63" t="n">
-        <v>11.01046167324793</v>
+        <v>10.98586685441511</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>45.40563383944395</v>
+        <v>45.42380288192529</v>
       </c>
       <c r="I64" t="n">
-        <v>12.33276348937222</v>
+        <v>12.28248322139378</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>45.43992754628905</v>
+        <v>45.42694164462185</v>
       </c>
       <c r="I65" t="n">
-        <v>12.3172430740662</v>
+        <v>12.28219361867837</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>45.46736032078812</v>
+        <v>45.38930900414127</v>
       </c>
       <c r="I66" t="n">
-        <v>10.95989666806104</v>
+        <v>10.97406401089688</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>45.43007894317405</v>
+        <v>45.45205803343016</v>
       </c>
       <c r="I67" t="n">
-        <v>11.85853904892121</v>
+        <v>11.87820014212608</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>45.56227790296602</v>
+        <v>45.52378801901811</v>
       </c>
       <c r="I68" t="n">
-        <v>11.50699844534957</v>
+        <v>11.57742393023254</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>45.58885042477604</v>
+        <v>45.57577403650354</v>
       </c>
       <c r="I69" t="n">
-        <v>11.49582283652866</v>
+        <v>11.5787075445803</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>45.54607690294638</v>
+        <v>45.50045591691055</v>
       </c>
       <c r="I70" t="n">
-        <v>11.57249520753876</v>
+        <v>11.56383133359826</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>45.50672594842224</v>
+        <v>45.54095822100361</v>
       </c>
       <c r="I71" t="n">
-        <v>11.5168021385895</v>
+        <v>11.59165531798094</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>45.54924621985229</v>
+        <v>45.5901846688996</v>
       </c>
       <c r="I72" t="n">
-        <v>11.56828299023293</v>
+        <v>11.57861466363811</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>45.56538233282634</v>
+        <v>45.58599235272514</v>
       </c>
       <c r="I73" t="n">
-        <v>11.50205955686925</v>
+        <v>11.58918467866261</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>45.51058466871057</v>
+        <v>45.56355682123213</v>
       </c>
       <c r="I74" t="n">
-        <v>11.52853738875991</v>
+        <v>11.52166304626273</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>45.52061073413583</v>
+        <v>45.55018669044272</v>
       </c>
       <c r="I75" t="n">
-        <v>11.54205440707192</v>
+        <v>11.56149794995895</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>45.52970921388652</v>
+        <v>45.54960242251548</v>
       </c>
       <c r="I76" t="n">
-        <v>11.5028662265868</v>
+        <v>11.56271612215622</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>45.41550295354491</v>
+        <v>45.40612651366183</v>
       </c>
       <c r="I77" t="n">
-        <v>12.32070099700627</v>
+        <v>12.31166017512852</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>45.4513710260451</v>
+        <v>45.43147482259386</v>
       </c>
       <c r="I78" t="n">
-        <v>11.8598376164491</v>
+        <v>11.86090314639996</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>45.39079308507591</v>
+        <v>45.36139842697055</v>
       </c>
       <c r="I79" t="n">
-        <v>11.9121318425567</v>
+        <v>11.8377090502165</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>45.39451267890669</v>
+        <v>45.44745602867025</v>
       </c>
       <c r="I80" t="n">
-        <v>11.91505727787202</v>
+        <v>11.92454294339201</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>45.53862209228125</v>
+        <v>45.4997706277453</v>
       </c>
       <c r="I81" t="n">
-        <v>11.56638921243799</v>
+        <v>11.52694892750597</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>45.57679321129844</v>
+        <v>45.56497222237699</v>
       </c>
       <c r="I82" t="n">
-        <v>11.54745809599001</v>
+        <v>11.54143916986996</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>45.39999092994532</v>
+        <v>45.37423704006719</v>
       </c>
       <c r="I83" t="n">
-        <v>11.92547138337442</v>
+        <v>11.82767453238398</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>45.50153788232874</v>
+        <v>45.51497076419402</v>
       </c>
       <c r="I84" t="n">
-        <v>11.49586063626295</v>
+        <v>11.57250994482773</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>45.4199823653298</v>
+        <v>45.43585302075641</v>
       </c>
       <c r="I85" t="n">
-        <v>12.34725155913963</v>
+        <v>12.26722122729284</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>45.54581417591036</v>
+        <v>45.52854833363518</v>
       </c>
       <c r="I86" t="n">
-        <v>11.58175705278726</v>
+        <v>11.57356709969397</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>45.52778098675017</v>
+        <v>45.59715572372757</v>
       </c>
       <c r="I87" t="n">
-        <v>11.58540376981586</v>
+        <v>11.5730068754176</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>45.44882730871826</v>
+        <v>45.43959182252329</v>
       </c>
       <c r="I88" t="n">
-        <v>12.31054310451355</v>
+        <v>12.3179044863</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>45.43790705404579</v>
+        <v>45.42873685968549</v>
       </c>
       <c r="I89" t="n">
-        <v>11.91776736743607</v>
+        <v>11.84758910996072</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>45.35657577138436</v>
+        <v>45.40196583855953</v>
       </c>
       <c r="I90" t="n">
-        <v>11.89686179764904</v>
+        <v>11.86824533366205</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>45.49999735214227</v>
+        <v>45.55174557450274</v>
       </c>
       <c r="I91" t="n">
-        <v>11.52108198734255</v>
+        <v>11.53094103129491</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>45.58367311617984</v>
+        <v>45.51608525532363</v>
       </c>
       <c r="I92" t="n">
-        <v>11.51125591855051</v>
+        <v>11.54590241235254</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>45.51356373589135</v>
+        <v>45.5333811305433</v>
       </c>
       <c r="I93" t="n">
-        <v>11.5014970820455</v>
+        <v>11.51447808121686</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45.45247965233014</v>
+        <v>45.44835283034138</v>
       </c>
       <c r="I94" t="n">
-        <v>11.92197579190063</v>
+        <v>11.92243765397179</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>45.36027722564396</v>
+        <v>45.42304829421111</v>
       </c>
       <c r="I95" t="n">
-        <v>11.88164174126515</v>
+        <v>11.84750489957948</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>45.43265170608289</v>
+        <v>45.48317031501985</v>
       </c>
       <c r="I96" t="n">
-        <v>12.31806857213436</v>
+        <v>12.31988741296238</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>45.55653132772095</v>
+        <v>45.5146141116312</v>
       </c>
       <c r="I97" t="n">
-        <v>11.50698894635483</v>
+        <v>11.53149917285251</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>45.5629339006837</v>
+        <v>45.51186376173073</v>
       </c>
       <c r="I98" t="n">
-        <v>11.49824833798291</v>
+        <v>11.57539846308679</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>45.56389763803676</v>
+        <v>45.49791350926126</v>
       </c>
       <c r="I99" t="n">
-        <v>11.52979121171647</v>
+        <v>11.58842506535872</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>45.58120584332152</v>
+        <v>45.54389862131126</v>
       </c>
       <c r="I100" t="n">
-        <v>11.56995104666269</v>
+        <v>11.56998441542495</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>45.5799131600111</v>
+        <v>45.50950107680003</v>
       </c>
       <c r="I101" t="n">
-        <v>11.57960433294404</v>
+        <v>11.50215909308355</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>45.53567900092341</v>
+        <v>45.55446783215851</v>
       </c>
       <c r="I102" t="n">
-        <v>11.5442641510773</v>
+        <v>11.51862951472959</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>45.44938471089736</v>
+        <v>45.38451448516841</v>
       </c>
       <c r="I103" t="n">
-        <v>11.91987023300477</v>
+        <v>11.82817188506748</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>45.54359879746031</v>
+        <v>45.58643860728831</v>
       </c>
       <c r="I104" t="n">
-        <v>11.52464000817636</v>
+        <v>11.56393229465978</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>45.53822596258754</v>
+        <v>45.51821713966697</v>
       </c>
       <c r="I105" t="n">
-        <v>11.49554743149196</v>
+        <v>11.57234478974233</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>45.67039205082061</v>
+        <v>45.66254093204451</v>
       </c>
       <c r="I106" t="n">
-        <v>12.28927880557318</v>
+        <v>12.2385523530891</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -6431,10 +6431,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>45.5966148457663</v>
+        <v>45.51665388294887</v>
       </c>
       <c r="I107" t="n">
-        <v>11.59225630863129</v>
+        <v>11.55385667567973</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -6487,10 +6487,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>45.5462432408696</v>
+        <v>45.56974544881707</v>
       </c>
       <c r="I108" t="n">
-        <v>11.50098622946067</v>
+        <v>11.58194309545047</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>45.51985666749313</v>
+        <v>45.53819021566494</v>
       </c>
       <c r="I109" t="n">
-        <v>11.57571666902058</v>
+        <v>11.51548237581501</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>45.41784922794241</v>
+        <v>45.40118148892511</v>
       </c>
       <c r="I110" t="n">
-        <v>11.90906702109483</v>
+        <v>11.84671028306105</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>45.55291718423936</v>
+        <v>45.54809943011527</v>
       </c>
       <c r="I111" t="n">
-        <v>11.57205332208549</v>
+        <v>11.57683884371839</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>45.39408012165605</v>
+        <v>45.38272241765974</v>
       </c>
       <c r="I112" t="n">
-        <v>11.83999746491271</v>
+        <v>11.84179257420525</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>45.36136157384926</v>
+        <v>45.40819289189341</v>
       </c>
       <c r="I113" t="n">
-        <v>11.8746798291424</v>
+        <v>11.8581880857476</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>45.45746382585096</v>
+        <v>45.48481008720231</v>
       </c>
       <c r="I114" t="n">
-        <v>10.95971614336474</v>
+        <v>10.98814689998412</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>45.45232578864352</v>
+        <v>45.38046194316956</v>
       </c>
       <c r="I116" t="n">
-        <v>11.91839419652693</v>
+        <v>11.85802061738671</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>45.53883984914739</v>
+        <v>45.52239118312987</v>
       </c>
       <c r="I117" t="n">
-        <v>11.52987781808892</v>
+        <v>11.54902184090547</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>45.51780846591225</v>
+        <v>45.53772515861009</v>
       </c>
       <c r="I118" t="n">
-        <v>11.53945901312915</v>
+        <v>11.52905728721917</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>45.37302629634058</v>
+        <v>45.4158521682992</v>
       </c>
       <c r="I119" t="n">
-        <v>11.9132426398246</v>
+        <v>11.86375914111254</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>45.40870446864458</v>
+        <v>45.36155883715509</v>
       </c>
       <c r="I120" t="n">
-        <v>11.87008846278466</v>
+        <v>11.85889753720416</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>45.51484391367462</v>
+        <v>45.58011509471896</v>
       </c>
       <c r="I121" t="n">
-        <v>11.59119176553394</v>
+        <v>11.5448730768351</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>45.54340109817999</v>
+        <v>45.5666796483541</v>
       </c>
       <c r="I122" t="n">
-        <v>11.57848506246064</v>
+        <v>11.54472403837381</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>45.58521485797156</v>
+        <v>45.5041589550561</v>
       </c>
       <c r="I123" t="n">
-        <v>11.57536227317164</v>
+        <v>11.50582325474111</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>45.52015298119495</v>
+        <v>45.5681828519746</v>
       </c>
       <c r="I124" t="n">
-        <v>11.49617844710473</v>
+        <v>11.52816242653823</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>45.36046373823645</v>
+        <v>45.42664785336429</v>
       </c>
       <c r="I125" t="n">
-        <v>11.90025788422965</v>
+        <v>11.91403182923532</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>45.4016334598108</v>
+        <v>45.37844718802308</v>
       </c>
       <c r="I126" t="n">
-        <v>11.89924535901416</v>
+        <v>11.83567310905736</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>45.42655924427193</v>
+        <v>45.44393362068354</v>
       </c>
       <c r="I127" t="n">
-        <v>12.34800922521867</v>
+        <v>12.31915966067802</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>45.5139636984498</v>
+        <v>45.56848977240485</v>
       </c>
       <c r="I128" t="n">
-        <v>11.51212017246924</v>
+        <v>11.57623084289722</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>45.43296625541579</v>
+        <v>45.38908167938936</v>
       </c>
       <c r="I129" t="n">
-        <v>11.88270178158305</v>
+        <v>11.83001589199794</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>45.42714554486383</v>
+        <v>45.42014239596796</v>
       </c>
       <c r="I130" t="n">
-        <v>11.86223373725511</v>
+        <v>11.89385266249748</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7771,10 +7771,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>45.65931535972054</v>
+        <v>45.6745541192682</v>
       </c>
       <c r="I131" t="n">
-        <v>12.29152988786786</v>
+        <v>12.29198290044885</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>45.40290641747457</v>
+        <v>45.46015943912038</v>
       </c>
       <c r="I132" t="n">
-        <v>12.29005436965421</v>
+        <v>12.33641917456987</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>45.56309389177496</v>
+        <v>45.49881409792306</v>
       </c>
       <c r="I133" t="n">
-        <v>11.55575027456366</v>
+        <v>11.51656184142672</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>45.36343076263967</v>
+        <v>45.42712239148255</v>
       </c>
       <c r="I134" t="n">
-        <v>11.87421122243451</v>
+        <v>11.86592800307823</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7989,17 +7989,9 @@
           <t>Carrè</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>45.51732904101443</v>
-      </c>
-      <c r="I135" t="n">
-        <v>11.57734365722946</v>
-      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>cucciolo</t>
@@ -8051,10 +8043,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>45.40026127032315</v>
+        <v>45.4445237071977</v>
       </c>
       <c r="I136" t="n">
-        <v>11.84486557339388</v>
+        <v>11.85671872969671</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -8107,10 +8099,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>45.58642123870843</v>
+        <v>45.51535161719262</v>
       </c>
       <c r="I137" t="n">
-        <v>11.51042882585593</v>
+        <v>11.52024526368519</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -8163,10 +8155,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>45.58733018415618</v>
+        <v>45.52420743431706</v>
       </c>
       <c r="I138" t="n">
-        <v>11.49654081375665</v>
+        <v>11.5523522501763</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -8219,10 +8211,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>45.55246943152046</v>
+        <v>45.58853671951663</v>
       </c>
       <c r="I139" t="n">
-        <v>11.56441924499645</v>
+        <v>11.59265455344492</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -8275,10 +8267,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>45.41930835864097</v>
+        <v>45.47407764998237</v>
       </c>
       <c r="I140" t="n">
-        <v>12.31806153114045</v>
+        <v>12.2859919103136</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -8331,10 +8323,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>45.47366635922968</v>
+        <v>45.47979208641413</v>
       </c>
       <c r="I141" t="n">
-        <v>12.27494440211583</v>
+        <v>12.26883471242774</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -8381,17 +8373,9 @@
           <t>Santorso</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>45.51722487863642</v>
-      </c>
-      <c r="I142" t="n">
-        <v>11.56642781741572</v>
-      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>cucciolo</t>
@@ -8443,10 +8427,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>45.52900063092233</v>
+        <v>45.51220328928375</v>
       </c>
       <c r="I143" t="n">
-        <v>11.49712165438506</v>
+        <v>11.55660506200705</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8499,10 +8483,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>45.56660655938342</v>
+        <v>45.55222714710217</v>
       </c>
       <c r="I144" t="n">
-        <v>11.56915274210449</v>
+        <v>11.55627312682076</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8555,10 +8539,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>45.58640916076038</v>
+        <v>45.50693417103908</v>
       </c>
       <c r="I145" t="n">
-        <v>11.50511736115612</v>
+        <v>11.54098235242515</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -8611,10 +8595,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>45.54457471153886</v>
+        <v>45.50988577066824</v>
       </c>
       <c r="I146" t="n">
-        <v>11.51995192680233</v>
+        <v>11.50601159771644</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -8667,10 +8651,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>45.52740348996969</v>
+        <v>45.59142773218514</v>
       </c>
       <c r="I147" t="n">
-        <v>11.55711041128547</v>
+        <v>11.59120211305772</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8723,10 +8707,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>45.57023064714861</v>
+        <v>45.5241334619926</v>
       </c>
       <c r="I148" t="n">
-        <v>11.50239575644232</v>
+        <v>11.54865246421715</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8775,10 +8759,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>45.54526248258834</v>
+        <v>45.5166015781036</v>
       </c>
       <c r="I149" t="n">
-        <v>11.52607332044118</v>
+        <v>11.52345682986263</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8831,10 +8815,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>45.51188767069736</v>
+        <v>45.56645550353142</v>
       </c>
       <c r="I150" t="n">
-        <v>11.57368839752712</v>
+        <v>11.55748381427141</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -8887,10 +8871,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>45.57179732567268</v>
+        <v>45.57808015857194</v>
       </c>
       <c r="I151" t="n">
-        <v>11.56651141812778</v>
+        <v>11.58302966671427</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8943,10 +8927,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>45.57692117342888</v>
+        <v>45.58534688276326</v>
       </c>
       <c r="I152" t="n">
-        <v>11.55410695649121</v>
+        <v>11.53842683276861</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8999,10 +8983,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>45.53827644443161</v>
+        <v>45.5318510500416</v>
       </c>
       <c r="I153" t="n">
-        <v>11.54671211798892</v>
+        <v>11.58365646294399</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -9055,10 +9039,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>45.56132019403443</v>
+        <v>45.54357922582794</v>
       </c>
       <c r="I154" t="n">
-        <v>11.58786477026825</v>
+        <v>11.53955014231866</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -9111,10 +9095,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>45.36193392028944</v>
+        <v>45.42998164223241</v>
       </c>
       <c r="I155" t="n">
-        <v>11.92061103270897</v>
+        <v>11.84112385994592</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -9167,10 +9151,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>45.43075101267686</v>
+        <v>45.44749418180777</v>
       </c>
       <c r="I156" t="n">
-        <v>12.36079660768651</v>
+        <v>12.33631877270279</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -9223,10 +9207,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>45.58417409829623</v>
+        <v>45.58843901976524</v>
       </c>
       <c r="I157" t="n">
-        <v>11.560694807215</v>
+        <v>11.49892966428809</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9331,10 +9315,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>45.43788991585531</v>
+        <v>45.39998795707997</v>
       </c>
       <c r="I159" t="n">
-        <v>11.86182654748831</v>
+        <v>11.90394689387699</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9387,10 +9371,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>45.62014212439082</v>
+        <v>45.64361918503048</v>
       </c>
       <c r="I160" t="n">
-        <v>12.2581394071484</v>
+        <v>12.22173189966023</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -9443,10 +9427,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>45.44899737544933</v>
+        <v>45.4491118194716</v>
       </c>
       <c r="I161" t="n">
-        <v>11.82743167995979</v>
+        <v>11.82997815254211</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -9495,10 +9479,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>45.5976774815585</v>
+        <v>45.58503404463162</v>
       </c>
       <c r="I162" t="n">
-        <v>11.50947703432977</v>
+        <v>11.5022820828739</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -9551,10 +9535,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>45.56808137524573</v>
+        <v>45.53558077848894</v>
       </c>
       <c r="I163" t="n">
-        <v>11.51860215287984</v>
+        <v>11.5605563565554</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9607,10 +9591,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>45.59113626414174</v>
+        <v>45.59264418649945</v>
       </c>
       <c r="I164" t="n">
-        <v>11.49862492843093</v>
+        <v>11.53786022437725</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -9667,10 +9651,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>45.35783905254792</v>
+        <v>45.41177976125962</v>
       </c>
       <c r="I165" t="n">
-        <v>11.89491426276013</v>
+        <v>11.85187537330898</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9723,10 +9707,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>45.57320101169929</v>
+        <v>45.53679341495733</v>
       </c>
       <c r="I166" t="n">
-        <v>11.53732350139227</v>
+        <v>11.57823820984</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9779,10 +9763,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>45.62298689833788</v>
+        <v>45.68689289207688</v>
       </c>
       <c r="I167" t="n">
-        <v>12.28594396126397</v>
+        <v>12.25452971378449</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9835,10 +9819,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>45.50998105844383</v>
+        <v>45.58567549298108</v>
       </c>
       <c r="I168" t="n">
-        <v>11.58812048062824</v>
+        <v>11.53799344066115</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -9891,10 +9875,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>45.37291657330506</v>
+        <v>45.43633152943838</v>
       </c>
       <c r="I169" t="n">
-        <v>11.92437386978452</v>
+        <v>11.89702888263338</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9947,10 +9931,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>45.6736636773977</v>
+        <v>45.69526461575903</v>
       </c>
       <c r="I170" t="n">
-        <v>12.24431223739889</v>
+        <v>12.22465475670767</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -10003,10 +9987,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>45.48686795649419</v>
+        <v>45.48603222230834</v>
       </c>
       <c r="I171" t="n">
-        <v>10.98459807188769</v>
+        <v>10.98140652934045</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -10059,10 +10043,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>45.57560461471269</v>
+        <v>45.57901229722267</v>
       </c>
       <c r="I172" t="n">
-        <v>11.51868776657751</v>
+        <v>11.58115069547673</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10115,10 +10099,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>45.54305328203684</v>
+        <v>45.52286834583753</v>
       </c>
       <c r="I173" t="n">
-        <v>11.51862495879765</v>
+        <v>11.54377802165451</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10171,10 +10155,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>45.59610492675705</v>
+        <v>45.59616369513132</v>
       </c>
       <c r="I174" t="n">
-        <v>11.55071018101946</v>
+        <v>11.58976636553671</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10227,10 +10211,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>45.6741780959582</v>
+        <v>45.66067960555407</v>
       </c>
       <c r="I175" t="n">
-        <v>12.23968792200065</v>
+        <v>12.21334047145831</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -10283,10 +10267,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>45.5091935818975</v>
+        <v>45.56558876744622</v>
       </c>
       <c r="I176" t="n">
-        <v>11.51298449347878</v>
+        <v>11.50983159070421</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10339,10 +10323,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>45.5415168299008</v>
+        <v>45.5465500469921</v>
       </c>
       <c r="I177" t="n">
-        <v>11.51873427836851</v>
+        <v>11.55851844754599</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -10395,10 +10379,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>45.37074721497059</v>
+        <v>45.36490961069684</v>
       </c>
       <c r="I178" t="n">
-        <v>11.89684786074365</v>
+        <v>11.90964730435952</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -10451,10 +10435,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>45.57769570453972</v>
+        <v>45.56645402876486</v>
       </c>
       <c r="I179" t="n">
-        <v>11.55662266691549</v>
+        <v>11.57848712919296</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10507,10 +10491,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>45.69263629607001</v>
+        <v>45.66376737351595</v>
       </c>
       <c r="I180" t="n">
-        <v>12.23876839123576</v>
+        <v>12.27674901692637</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -10563,10 +10547,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>45.55725303121752</v>
+        <v>45.55298973775317</v>
       </c>
       <c r="I181" t="n">
-        <v>11.5169222799238</v>
+        <v>11.57378565884534</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -10619,10 +10603,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>45.58627184423533</v>
+        <v>45.53036694726358</v>
       </c>
       <c r="I182" t="n">
-        <v>11.5075224384455</v>
+        <v>11.49904740410179</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -10675,10 +10659,10 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>45.67820734643198</v>
+        <v>45.66955416903522</v>
       </c>
       <c r="I183" t="n">
-        <v>12.26864998386568</v>
+        <v>12.25483965015049</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -10783,10 +10767,10 @@
         </is>
       </c>
       <c r="H185" t="n">
-        <v>45.38406312432942</v>
+        <v>45.4234131032881</v>
       </c>
       <c r="I185" t="n">
-        <v>11.86156619533663</v>
+        <v>11.84817683435851</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -10839,10 +10823,10 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>45.36377061726274</v>
+        <v>45.37360629624386</v>
       </c>
       <c r="I186" t="n">
-        <v>11.84701228497196</v>
+        <v>11.89864768347854</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -10895,10 +10879,10 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>45.58025775230278</v>
+        <v>45.52173264915437</v>
       </c>
       <c r="I187" t="n">
-        <v>11.52364601876993</v>
+        <v>11.59181393297679</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -10951,10 +10935,10 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>45.57308497400562</v>
+        <v>45.51127316959194</v>
       </c>
       <c r="I188" t="n">
-        <v>11.52852338975896</v>
+        <v>11.56851511001798</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -11007,10 +10991,10 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>45.58929359902974</v>
+        <v>45.52605872215928</v>
       </c>
       <c r="I189" t="n">
-        <v>11.52444436880327</v>
+        <v>11.5345338531029</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -11063,10 +11047,10 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>45.53509197566033</v>
+        <v>45.57065222710738</v>
       </c>
       <c r="I190" t="n">
-        <v>11.50695154720949</v>
+        <v>11.54904663462314</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -11119,10 +11103,10 @@
         </is>
       </c>
       <c r="H191" t="n">
-        <v>45.58395374514986</v>
+        <v>45.50100508300459</v>
       </c>
       <c r="I191" t="n">
-        <v>11.53510637503526</v>
+        <v>11.58949717788213</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -11175,10 +11159,10 @@
         </is>
       </c>
       <c r="H192" t="n">
-        <v>45.63733779724765</v>
+        <v>45.70328162462787</v>
       </c>
       <c r="I192" t="n">
-        <v>12.2118155178889</v>
+        <v>12.23333732680687</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -11231,10 +11215,10 @@
         </is>
       </c>
       <c r="H193" t="n">
-        <v>45.48656056028926</v>
+        <v>45.40363785589561</v>
       </c>
       <c r="I193" t="n">
-        <v>12.29791652794114</v>
+        <v>12.27792353576556</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -11287,10 +11271,10 @@
         </is>
       </c>
       <c r="H194" t="n">
-        <v>45.44497725014617</v>
+        <v>45.39587765817384</v>
       </c>
       <c r="I194" t="n">
-        <v>11.92448139091926</v>
+        <v>11.87572983028032</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -11343,10 +11327,10 @@
         </is>
       </c>
       <c r="H195" t="n">
-        <v>45.53404134875714</v>
+        <v>45.5530098387316</v>
       </c>
       <c r="I195" t="n">
-        <v>11.50107013978303</v>
+        <v>11.49550840353361</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -11399,10 +11383,10 @@
         </is>
       </c>
       <c r="H196" t="n">
-        <v>45.39854300986422</v>
+        <v>45.45133570117293</v>
       </c>
       <c r="I196" t="n">
-        <v>11.89607652137967</v>
+        <v>11.88375824283951</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -11455,10 +11439,10 @@
         </is>
       </c>
       <c r="H197" t="n">
-        <v>45.39642979430746</v>
+        <v>45.43783105522845</v>
       </c>
       <c r="I197" t="n">
-        <v>11.86045399961248</v>
+        <v>11.87100959774133</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -11511,10 +11495,10 @@
         </is>
       </c>
       <c r="H198" t="n">
-        <v>45.57460651315871</v>
+        <v>45.50122804109356</v>
       </c>
       <c r="I198" t="n">
-        <v>11.52192344179589</v>
+        <v>11.56831753579301</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="n">
@@ -11563,10 +11547,10 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>45.6453949208295</v>
+        <v>45.65106655200425</v>
       </c>
       <c r="I199" t="n">
-        <v>12.24938884290225</v>
+        <v>12.22684875246339</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -11615,10 +11599,10 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>45.56711972060499</v>
+        <v>45.54267513510737</v>
       </c>
       <c r="I200" t="n">
-        <v>11.52170823392346</v>
+        <v>11.5852553506783</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -11671,10 +11655,10 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>45.44932115170599</v>
+        <v>45.41410080771553</v>
       </c>
       <c r="I201" t="n">
-        <v>11.84020163456573</v>
+        <v>11.8769369213795</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -11727,10 +11711,10 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>45.52774969309989</v>
+        <v>45.58261971669562</v>
       </c>
       <c r="I202" t="n">
-        <v>11.52952846188877</v>
+        <v>11.57808275480635</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -11783,10 +11767,10 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>45.44156269752753</v>
+        <v>45.44221143490089</v>
       </c>
       <c r="I203" t="n">
-        <v>12.3484479945947</v>
+        <v>12.32942317898853</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -11839,10 +11823,10 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>45.5896240716889</v>
+        <v>45.5942746296661</v>
       </c>
       <c r="I204" t="n">
-        <v>11.49621006498065</v>
+        <v>11.55596382170885</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -11895,10 +11879,10 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>45.38284857453566</v>
+        <v>45.43999683713052</v>
       </c>
       <c r="I205" t="n">
-        <v>11.90926592835529</v>
+        <v>11.92313887805316</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -11951,10 +11935,10 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>45.52690411333301</v>
+        <v>45.54756982336438</v>
       </c>
       <c r="I206" t="n">
-        <v>11.57283329896229</v>
+        <v>11.50226262060308</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -12059,10 +12043,10 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>45.56330585730014</v>
+        <v>45.58918185208231</v>
       </c>
       <c r="I208" t="n">
-        <v>11.51706443766183</v>
+        <v>11.58961428817452</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -12115,10 +12099,10 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>45.57061487900408</v>
+        <v>45.52174099819236</v>
       </c>
       <c r="I209" t="n">
-        <v>11.49706013937729</v>
+        <v>11.58352656338116</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -12171,10 +12155,10 @@
         </is>
       </c>
       <c r="H210" t="n">
-        <v>45.58477092718733</v>
+        <v>45.50156686504408</v>
       </c>
       <c r="I210" t="n">
-        <v>11.56352037384877</v>
+        <v>11.56587534660936</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -12227,10 +12211,10 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>45.42240375076236</v>
+        <v>45.42127153803388</v>
       </c>
       <c r="I211" t="n">
-        <v>11.86803356117889</v>
+        <v>11.8933659988405</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -12283,10 +12267,10 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>45.54242980682015</v>
+        <v>45.55794278127709</v>
       </c>
       <c r="I212" t="n">
-        <v>11.58187539205549</v>
+        <v>11.52445841974882</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -12339,10 +12323,10 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>45.44415171878632</v>
+        <v>45.43212763088918</v>
       </c>
       <c r="I213" t="n">
-        <v>11.87998451226885</v>
+        <v>11.83637770218353</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -12395,10 +12379,10 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>45.50913065035773</v>
+        <v>45.52866760716925</v>
       </c>
       <c r="I214" t="n">
-        <v>11.56823449660641</v>
+        <v>11.58966714643913</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -12455,10 +12439,10 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>45.49815309942769</v>
+        <v>45.54517503672054</v>
       </c>
       <c r="I215" t="n">
-        <v>11.56597945753998</v>
+        <v>11.50959860871485</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12515,10 +12499,10 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>45.50577289685192</v>
+        <v>45.54506057026556</v>
       </c>
       <c r="I216" t="n">
-        <v>11.49719201040022</v>
+        <v>11.50370722601443</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -12571,10 +12555,10 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>45.4399945582291</v>
+        <v>45.37376783965404</v>
       </c>
       <c r="I217" t="n">
-        <v>11.90213922221896</v>
+        <v>11.90035740511972</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -12627,10 +12611,10 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>45.55299676566214</v>
+        <v>45.5037179782417</v>
       </c>
       <c r="I218" t="n">
-        <v>11.50882962915484</v>
+        <v>11.50866697989738</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -12683,10 +12667,10 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>45.52069153298542</v>
+        <v>45.59720826022676</v>
       </c>
       <c r="I219" t="n">
-        <v>11.50673550113981</v>
+        <v>11.54575604138496</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -12743,10 +12727,10 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>45.5111700067584</v>
+        <v>45.51227770060809</v>
       </c>
       <c r="I220" t="n">
-        <v>11.51619934045815</v>
+        <v>11.58028652623733</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -12799,10 +12783,10 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>45.51119985826715</v>
+        <v>45.50650340032722</v>
       </c>
       <c r="I221" t="n">
-        <v>11.53345526805481</v>
+        <v>11.51892568336774</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -12855,10 +12839,10 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>45.5727390607039</v>
+        <v>45.50642746815059</v>
       </c>
       <c r="I222" t="n">
-        <v>11.53834524299318</v>
+        <v>11.51078917019004</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -12963,10 +12947,10 @@
         </is>
       </c>
       <c r="H224" t="n">
-        <v>45.51891137018011</v>
+        <v>45.49849505270014</v>
       </c>
       <c r="I224" t="n">
-        <v>11.53467314646589</v>
+        <v>11.54765496637389</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -13013,17 +12997,9 @@
           <t>Sossano</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="H225" t="n">
-        <v>45.58468152873789</v>
-      </c>
-      <c r="I225" t="n">
-        <v>11.54923228109381</v>
-      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>adulto</t>
@@ -13075,10 +13051,10 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>45.51042574806578</v>
+        <v>45.58443082928317</v>
       </c>
       <c r="I226" t="n">
-        <v>11.54073460440157</v>
+        <v>11.57826162480449</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -13131,10 +13107,10 @@
         </is>
       </c>
       <c r="H227" t="n">
-        <v>45.59775156866026</v>
+        <v>45.52024979885379</v>
       </c>
       <c r="I227" t="n">
-        <v>11.566895156165</v>
+        <v>11.52587233730721</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -13187,10 +13163,10 @@
         </is>
       </c>
       <c r="H228" t="n">
-        <v>45.51133549909413</v>
+        <v>45.57123877511381</v>
       </c>
       <c r="I228" t="n">
-        <v>11.49900429614956</v>
+        <v>11.56628402093287</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -13243,10 +13219,10 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>45.57825115308104</v>
+        <v>45.55399608530483</v>
       </c>
       <c r="I229" t="n">
-        <v>11.53241746493717</v>
+        <v>11.58003213552871</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -13299,10 +13275,10 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>45.38948001786672</v>
+        <v>45.43622751249892</v>
       </c>
       <c r="I230" t="n">
-        <v>11.90860718216777</v>
+        <v>11.90666590450052</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -13355,10 +13331,10 @@
         </is>
       </c>
       <c r="H231" t="n">
-        <v>45.43673398799299</v>
+        <v>45.48504551063338</v>
       </c>
       <c r="I231" t="n">
-        <v>12.35601005680946</v>
+        <v>12.2659018657852</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13411,10 +13387,10 @@
         </is>
       </c>
       <c r="H232" t="n">
-        <v>45.41424626621131</v>
+        <v>45.36954799528716</v>
       </c>
       <c r="I232" t="n">
-        <v>11.90784706228434</v>
+        <v>11.88684965837305</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -13467,10 +13443,10 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>45.44624449706544</v>
+        <v>45.42819934669198</v>
       </c>
       <c r="I233" t="n">
-        <v>12.34217849616867</v>
+        <v>12.34712624558524</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -13523,10 +13499,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>45.41901577625215</v>
+        <v>45.36684466703157</v>
       </c>
       <c r="I234" t="n">
-        <v>11.87494288447549</v>
+        <v>11.92051057517748</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13579,10 +13555,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>45.45562547858717</v>
+        <v>45.3812503283941</v>
       </c>
       <c r="I235" t="n">
-        <v>11.8569026737149</v>
+        <v>11.88910990375812</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13635,10 +13611,10 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>45.39944937192645</v>
+        <v>45.44980796652974</v>
       </c>
       <c r="I236" t="n">
-        <v>11.88815598974344</v>
+        <v>11.86487252209042</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -13691,10 +13667,10 @@
         </is>
       </c>
       <c r="H237" t="n">
-        <v>45.55373706662067</v>
+        <v>45.50026686298879</v>
       </c>
       <c r="I237" t="n">
-        <v>11.56323821978222</v>
+        <v>11.57365357636955</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -13751,10 +13727,10 @@
         </is>
       </c>
       <c r="H238" t="n">
-        <v>45.4403839781475</v>
+        <v>45.42946323328427</v>
       </c>
       <c r="I238" t="n">
-        <v>11.91007921760382</v>
+        <v>11.87531906357259</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -13811,10 +13787,10 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>45.44611818486782</v>
+        <v>45.35824490549194</v>
       </c>
       <c r="I239" t="n">
-        <v>11.8442734482106</v>
+        <v>11.8953251912311</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -13867,10 +13843,10 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>45.50914183796562</v>
+        <v>45.57606609215763</v>
       </c>
       <c r="I240" t="n">
-        <v>11.56513545009469</v>
+        <v>11.52315795402445</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -13923,10 +13899,10 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>45.65099566270158</v>
+        <v>45.66726015144712</v>
       </c>
       <c r="I241" t="n">
-        <v>12.24482591597765</v>
+        <v>12.28316696585205</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>

--- a/web/Pipistrelli 2025.xlsx
+++ b/web/Pipistrelli 2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45659</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -550,10 +550,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,10 +609,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,7 +624,6 @@
           <t>Myotis emarginatus</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -666,10 +663,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -682,7 +678,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Santorso </t>
@@ -722,10 +717,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -738,7 +732,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Caltrano</t>
@@ -778,10 +771,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -809,7 +801,11 @@
           <t>Costabissara</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.5855421</v>
       </c>
@@ -834,10 +830,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45675</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -850,7 +845,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Venezia</t>
@@ -890,10 +884,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -906,7 +899,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Modena</t>
@@ -917,7 +909,11 @@
           <t>Modena</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>44.5384728</v>
       </c>
@@ -942,10 +938,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -958,7 +953,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Montecchio maggiore </t>
@@ -998,10 +992,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1014,7 +1007,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -1049,11 +1041,9 @@
           <t>Trovato nella casa di montagna,in terra,chiuso probabilmente dall'autunno, le guardie forestali di Schio lo hanno fatto mettere in giardino in pieno giorno.</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1066,7 +1056,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -1106,10 +1095,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1166,10 +1154,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1182,7 +1169,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Montecchio maggiore</t>
@@ -1222,10 +1208,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1238,7 +1223,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1278,10 +1262,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1294,7 +1277,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1334,10 +1316,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1350,7 +1331,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -1361,7 +1341,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>45.4746344</v>
       </c>
@@ -1386,10 +1370,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1402,7 +1385,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Piazza Guglielmo Marconi</t>
@@ -1437,11 +1419,9 @@
           <t>Segnalato pipistrello dentro la chiesa</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1469,7 +1449,11 @@
           <t xml:space="preserve">Castegnero </t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>45.4424748</v>
       </c>
@@ -1494,10 +1478,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1510,7 +1493,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -1550,10 +1532,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1610,10 +1591,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1641,7 +1621,11 @@
           <t>Isola Vicentina</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>45.6286685</v>
       </c>
@@ -1666,10 +1650,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1726,10 +1709,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1742,7 +1724,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Scandolara</t>
@@ -1782,10 +1763,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1798,7 +1778,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Lido</t>
@@ -1838,10 +1817,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1854,7 +1832,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Modica</t>
@@ -1865,7 +1842,11 @@
           <t>Ragusa</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RG</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>36.8589209</v>
       </c>
@@ -1890,10 +1871,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1950,10 +1930,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1981,7 +1960,11 @@
           <t>Trento</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>46.0533463</v>
       </c>
@@ -2006,10 +1989,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45780</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2022,7 +2004,6 @@
           <t>Vespertilio murinus</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2062,10 +2043,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2078,7 +2058,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Terrassa Padovana</t>
@@ -2118,10 +2097,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2134,7 +2112,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -2174,10 +2151,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2190,7 +2166,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -2230,10 +2205,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2246,7 +2220,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -2257,7 +2230,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>45.6355174</v>
       </c>
@@ -2282,10 +2259,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2298,7 +2274,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2338,10 +2313,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45812</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2354,7 +2328,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2394,10 +2367,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2410,7 +2382,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Creazzo</t>
@@ -2450,10 +2421,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2466,7 +2436,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Via Brigata orobica 9</t>
@@ -2477,7 +2446,11 @@
           <t>Camisano vicentino</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>45.5220266</v>
       </c>
@@ -2502,10 +2475,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2518,7 +2490,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Via Andrea Moschetti 7</t>
@@ -2558,10 +2529,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2574,7 +2544,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Bergamo</t>
@@ -2585,7 +2554,11 @@
           <t>Bergamo</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>45.7566557</v>
       </c>
@@ -2615,7 +2588,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2628,7 +2601,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Largo Europa</t>
@@ -2639,7 +2611,11 @@
           <t>Pojana Maggiore</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>45.2937911</v>
       </c>
@@ -2664,10 +2640,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2680,7 +2655,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Largo Europa</t>
@@ -2691,7 +2665,11 @@
           <t>Pojana Maggiore</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>45.2937911</v>
       </c>
@@ -2716,10 +2694,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2732,7 +2709,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Piazzola sul Brenta</t>
@@ -2772,10 +2748,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2788,7 +2763,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Via Corelli</t>
@@ -2828,10 +2802,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2888,10 +2861,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2904,7 +2876,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -2944,10 +2915,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2960,7 +2930,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -3005,7 +2974,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3018,7 +2987,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Via Aulo Gellio Valle 23</t>
@@ -3058,10 +3026,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3074,7 +3041,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Via Aulo Gellio Valle 23</t>
@@ -3114,10 +3080,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3130,7 +3095,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Via Baracche</t>
@@ -3141,7 +3105,11 @@
           <t>Tezze sul Brenta</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>45.6893479</v>
       </c>
@@ -3166,10 +3134,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3197,7 +3164,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>45.7244163</v>
       </c>
@@ -3222,10 +3193,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3238,7 +3208,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -3249,7 +3218,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>45.7244163</v>
       </c>
@@ -3274,10 +3247,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3290,7 +3262,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -3301,7 +3272,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>45.7244163</v>
       </c>
@@ -3326,10 +3301,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3342,7 +3316,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile, 18/5</t>
@@ -3382,10 +3355,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3398,7 +3370,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Campagna Lupia</t>
@@ -3409,7 +3380,11 @@
           <t>Campagna Lupia</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>45.3536125</v>
       </c>
@@ -3434,10 +3409,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3450,7 +3424,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3490,10 +3463,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3506,7 +3478,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>San Pietro in Gu</t>
@@ -3517,7 +3488,11 @@
           <t>San Pietro in Gu</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>45.6140864</v>
       </c>
@@ -3542,10 +3517,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3558,7 +3532,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Adria</t>
@@ -3598,10 +3571,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3614,7 +3586,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Adria</t>
@@ -3654,10 +3625,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3670,7 +3640,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -3710,10 +3679,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3726,7 +3694,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">Martellago </t>
@@ -3737,7 +3704,11 @@
           <t xml:space="preserve">Martellago </t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>45.537998</v>
       </c>
@@ -3762,10 +3733,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3778,7 +3748,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">Martellago </t>
@@ -3789,7 +3758,11 @@
           <t xml:space="preserve">Martellago </t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>45.537998</v>
       </c>
@@ -3814,10 +3787,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3830,7 +3802,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -3870,10 +3841,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3886,7 +3856,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Cittadella</t>
@@ -3926,10 +3895,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3942,7 +3910,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Via Thaon di Revel 36</t>
@@ -3982,10 +3949,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3998,7 +3964,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -4038,10 +4003,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4054,7 +4018,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4065,7 +4028,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>45.4437746</v>
       </c>
@@ -4090,10 +4057,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4106,7 +4072,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4117,7 +4082,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>45.4437746</v>
       </c>
@@ -4142,10 +4111,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4158,7 +4126,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4169,7 +4136,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>45.4437746</v>
       </c>
@@ -4194,10 +4165,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4210,7 +4180,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4221,7 +4190,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>45.4437746</v>
       </c>
@@ -4246,10 +4219,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4262,7 +4234,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4273,7 +4244,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>45.4437746</v>
       </c>
@@ -4298,10 +4273,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4314,7 +4288,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4325,7 +4298,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>45.4437746</v>
       </c>
@@ -4350,10 +4327,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4366,7 +4342,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Montegalda</t>
@@ -4377,7 +4352,11 @@
           <t>Montegalda</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>45.4437746</v>
       </c>
@@ -4402,10 +4381,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4418,7 +4396,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Via Pazzana 1</t>
@@ -4458,10 +4435,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4474,7 +4450,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Arcella</t>
@@ -4514,10 +4489,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4530,7 +4504,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -4541,7 +4514,11 @@
           <t>Villanova di Camposampiero</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>45.4904556</v>
       </c>
@@ -4571,7 +4548,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4584,7 +4561,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -4595,7 +4571,11 @@
           <t>Villanova di Camposampiero</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>45.4904556</v>
       </c>
@@ -4620,10 +4600,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4636,7 +4615,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Via Pepe 10</t>
@@ -4647,7 +4625,6 @@
           <t>Povolaro di Dueville</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>45.6268991</v>
       </c>
@@ -4672,10 +4649,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4688,7 +4664,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Breganze</t>
@@ -4699,7 +4674,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>45.7081441</v>
       </c>
@@ -4729,7 +4708,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4742,7 +4721,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Torreglia</t>
@@ -4753,7 +4731,11 @@
           <t>Torreglia</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>45.3356668</v>
       </c>
@@ -4778,10 +4760,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4794,7 +4775,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Altopiano di Asiago</t>
@@ -4805,7 +4785,11 @@
           <t>Asiago</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>45.8523602</v>
       </c>
@@ -4830,10 +4814,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4846,7 +4829,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Via delle industrie 2/c</t>
@@ -4886,10 +4868,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4902,7 +4883,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Bassano del Grappa</t>
@@ -4942,10 +4922,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4958,7 +4937,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Cassola</t>
@@ -4969,7 +4947,11 @@
           <t>Cassola</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>45.7327961</v>
       </c>
@@ -4994,10 +4976,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5010,7 +4991,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Santa Maria Di Sala</t>
@@ -5021,7 +5001,11 @@
           <t>Santa Maria Di Sala</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>45.5054111</v>
       </c>
@@ -5046,10 +5030,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5062,7 +5045,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Cinto Euganeo</t>
@@ -5073,7 +5055,11 @@
           <t>Cinto Euganeo</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H85" t="n">
         <v>45.2894673</v>
       </c>
@@ -5098,10 +5084,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5114,7 +5099,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Cinto Euganeo</t>
@@ -5125,7 +5109,11 @@
           <t>Cinto Euganeo</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>45.2894673</v>
       </c>
@@ -5150,10 +5138,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5166,7 +5153,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Zanon</t>
@@ -5206,10 +5192,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5222,7 +5207,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Via Zanon</t>
@@ -5262,10 +5246,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45826</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5278,7 +5261,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -5318,10 +5300,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5334,7 +5315,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Pascoli 16</t>
@@ -5374,10 +5354,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5390,7 +5369,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Via Meldelssohn 2/B</t>
@@ -5430,10 +5408,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5446,7 +5423,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Pianiga</t>
@@ -5457,7 +5433,11 @@
           <t>Pianiga</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>45.4559602</v>
       </c>
@@ -5482,10 +5462,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5498,7 +5477,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Via San Lazzaro 41</t>
@@ -5538,10 +5516,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5554,7 +5531,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Via San Lazzaro 41</t>
@@ -5594,10 +5570,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -5610,7 +5585,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Strada delle Cattane, 16</t>
@@ -5650,10 +5624,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -5666,7 +5639,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Contrada Valdicase 11</t>
@@ -5677,7 +5649,6 @@
           <t>Valle di Castelgomberto</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>45.5852389</v>
       </c>
@@ -5702,10 +5673,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -5718,7 +5688,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -5729,7 +5698,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>45.4746344</v>
       </c>
@@ -5754,10 +5727,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -5770,7 +5742,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>San Vito di Leguzzano</t>
@@ -5781,7 +5752,11 @@
           <t>San Vito di Leguzzano</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>45.6815519</v>
       </c>
@@ -5806,10 +5781,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -5822,7 +5796,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -5862,10 +5835,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -5878,7 +5850,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Pianezze</t>
@@ -5889,7 +5860,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>45.4792746</v>
       </c>
@@ -5914,10 +5889,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -5930,7 +5904,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -5970,10 +5943,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -5986,7 +5958,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Preganziol</t>
@@ -5997,7 +5968,11 @@
           <t>Preganziol</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>45.6025304</v>
       </c>
@@ -6022,10 +5997,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -6038,7 +6012,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6049,7 +6022,11 @@
           <t>Marano vicentino</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>45.7038592</v>
       </c>
@@ -6074,10 +6051,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -6090,7 +6066,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6101,7 +6076,11 @@
           <t>Marano vicentino</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>45.7038592</v>
       </c>
@@ -6126,10 +6105,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45830</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6142,7 +6120,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Santa Lucia 51</t>
@@ -6153,7 +6130,11 @@
           <t>Marano vicentino</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>45.6950009</v>
       </c>
@@ -6178,10 +6159,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6194,7 +6174,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Via Raccola 17</t>
@@ -6205,7 +6184,11 @@
           <t>Galzignano Terme</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>45.3123486</v>
       </c>
@@ -6230,10 +6213,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6246,7 +6228,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -6286,10 +6267,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6302,7 +6282,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Forcellini 172 </t>
@@ -6342,10 +6321,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6358,7 +6336,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Via Vallazza 15</t>
@@ -6369,7 +6346,11 @@
           <t>Boara Pisani</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>45.130809</v>
       </c>
@@ -6394,10 +6375,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6410,7 +6390,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -6450,10 +6429,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -6466,7 +6444,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Via Porte di Sopra, 65B</t>
@@ -6477,7 +6454,11 @@
           <t>Lendinara</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>45.0849847</v>
       </c>
@@ -6502,10 +6483,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45832</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -6518,7 +6498,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Via Montà</t>
@@ -6558,10 +6537,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -6574,7 +6552,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Sarcedo</t>
@@ -6585,7 +6562,11 @@
           <t>Sarcedo</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>45.7078513</v>
       </c>
@@ -6610,10 +6591,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -6626,7 +6606,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Sarcedo</t>
@@ -6637,7 +6616,11 @@
           <t>Sarcedo</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>45.7078513</v>
       </c>
@@ -6662,10 +6645,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -6678,7 +6660,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Villanova di Camposampiero</t>
@@ -6689,7 +6670,11 @@
           <t>Villanova di Camposampiero</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>45.4904556</v>
       </c>
@@ -6714,10 +6699,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -6730,7 +6714,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Carmignano di Brenta</t>
@@ -6741,7 +6724,11 @@
           <t>Carmignano di Brenta</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>45.6287707</v>
       </c>
@@ -6766,10 +6753,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -6782,7 +6768,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6822,10 +6807,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -6838,7 +6822,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Via Ruspoli</t>
@@ -6878,10 +6861,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -6894,7 +6876,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Contrada Valdicese 11</t>
@@ -6905,7 +6886,6 @@
           <t>Valle di Castelgomberto</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>45.5852389</v>
       </c>
@@ -6930,10 +6910,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -6946,7 +6925,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Zanè</t>
@@ -6957,7 +6935,11 @@
           <t>Zanè</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>45.7201187</v>
       </c>
@@ -6982,10 +6964,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -6998,7 +6979,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Ponte San Nicolò</t>
@@ -7009,7 +6989,11 @@
           <t>Ponte San Nicolò</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>45.3652389</v>
       </c>
@@ -7034,10 +7018,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -7050,7 +7033,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Este</t>
@@ -7090,10 +7072,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -7106,7 +7087,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Eraclea</t>
@@ -7117,7 +7097,11 @@
           <t>Eraclea</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>45.5762676</v>
       </c>
@@ -7142,10 +7126,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -7158,7 +7141,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Lonigo</t>
@@ -7169,7 +7151,11 @@
           <t>Lonigo</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>45.3881155</v>
       </c>
@@ -7194,10 +7180,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -7210,7 +7195,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -7250,10 +7234,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -7266,7 +7249,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Ponte San Nicolò</t>
@@ -7277,7 +7259,11 @@
           <t>Ponte San Nicolò</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>45.3652389</v>
       </c>
@@ -7302,10 +7288,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -7318,7 +7303,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Preganziol</t>
@@ -7329,7 +7313,11 @@
           <t>Preganziol</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>45.6025304</v>
       </c>
@@ -7354,10 +7342,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -7370,7 +7357,6 @@
           <t>Pipistrellus nathusii</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Cavallino-Treporti</t>
@@ -7381,7 +7367,11 @@
           <t>Cavallino-Treporti</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>45.4792171</v>
       </c>
@@ -7406,10 +7396,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -7422,7 +7411,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -7433,7 +7421,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>45.6355174</v>
       </c>
@@ -7458,10 +7450,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45836</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -7474,7 +7465,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Carmignano di Brenta</t>
@@ -7485,7 +7475,11 @@
           <t>Carmignano di Brenta</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>45.6287707</v>
       </c>
@@ -7510,10 +7504,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -7526,7 +7519,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Via Tedesca 69</t>
@@ -7537,7 +7529,11 @@
           <t>Carrè</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>45.746597</v>
       </c>
@@ -7562,10 +7558,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -7578,7 +7573,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Montegrotto</t>
@@ -7589,7 +7583,6 @@
           <t>Montegrotto</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>45.331491</v>
       </c>
@@ -7614,10 +7607,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -7630,7 +7622,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Contrà Torretti 45</t>
@@ -7670,10 +7661,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -7686,7 +7676,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -7697,7 +7686,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>45.6606078</v>
       </c>
@@ -7722,10 +7715,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -7738,7 +7730,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Via Mazzini 15</t>
@@ -7749,7 +7740,11 @@
           <t>Breganze</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>45.7081441</v>
       </c>
@@ -7774,10 +7769,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -7790,7 +7784,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Mirano</t>
@@ -7830,10 +7823,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -7846,7 +7838,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Fiesso d'Artico</t>
@@ -7857,7 +7848,11 @@
           <t>Fiesso d'Artico</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>45.4167857</v>
       </c>
@@ -7882,10 +7877,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -7898,7 +7892,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Via dei Roveri 16</t>
@@ -7938,10 +7931,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -7954,7 +7946,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>Recoaro Terme</t>
@@ -7994,10 +7985,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -8010,7 +8000,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>Via Giambattista Vico 146</t>
@@ -8050,10 +8039,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -8066,7 +8054,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -8106,10 +8093,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -8122,7 +8108,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Brendola</t>
@@ -8133,7 +8118,11 @@
           <t>Brendola</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>45.4721218</v>
       </c>
@@ -8158,10 +8147,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -8174,7 +8162,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Pertile 18 </t>
@@ -8214,10 +8201,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -8230,7 +8216,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t xml:space="preserve">Via Fornace 84 </t>
@@ -8241,7 +8226,11 @@
           <t>Costabissara</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>45.5792261</v>
       </c>
@@ -8261,11 +8250,9 @@
           <t>Debilitato lasciato in una siepe</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -8278,7 +8265,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Recoaro Terme</t>
@@ -8318,10 +8304,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -8334,7 +8319,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -8345,7 +8329,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>45.6606078</v>
       </c>
@@ -8370,10 +8358,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -8386,7 +8373,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Via Donizetti 7</t>
@@ -8397,7 +8383,11 @@
           <t>Dueville</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>45.6400579</v>
       </c>
@@ -8422,10 +8412,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -8438,7 +8427,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -8478,10 +8466,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -8494,7 +8481,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Rosà</t>
@@ -8505,7 +8491,11 @@
           <t>Rosà</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>45.7244163</v>
       </c>
@@ -8530,10 +8520,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -8546,7 +8535,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Campedello</t>
@@ -8586,10 +8574,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -8602,7 +8589,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Vigonza</t>
@@ -8642,10 +8628,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -8658,7 +8643,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Via Musil 18</t>
@@ -8698,10 +8682,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -8714,7 +8697,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -8725,7 +8707,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H153" t="n">
         <v>45.5004723</v>
       </c>
@@ -8750,10 +8736,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -8766,7 +8751,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Bolzano Vicentino</t>
@@ -8806,10 +8790,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -8822,7 +8805,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Lozzo Atestino</t>
@@ -8833,7 +8815,11 @@
           <t>Lozzo Atestino</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H155" t="n">
         <v>45.2909178</v>
       </c>
@@ -8858,10 +8844,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -8874,7 +8859,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Treviso</t>
@@ -8914,10 +8898,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -8930,7 +8913,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Selvazzano Dentro</t>
@@ -8970,10 +8952,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -8981,8 +8962,6 @@
           <t>20:08:00</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -9022,10 +9001,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -9038,7 +9016,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Via Vivaldi 5</t>
@@ -9049,7 +9026,11 @@
           <t>Costabissara</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H159" t="n">
         <v>45.5818027</v>
       </c>
@@ -9074,10 +9055,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -9090,7 +9070,6 @@
           <t>Rhinolophus hipposideros</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Valstagna</t>
@@ -9101,7 +9080,11 @@
           <t>Valbrenta</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H160" t="n">
         <v>45.8599717</v>
       </c>
@@ -9126,10 +9109,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -9157,7 +9139,11 @@
           <t>Piazzola sul Brenta</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H161" t="n">
         <v>45.541496</v>
       </c>
@@ -9182,10 +9168,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -9198,7 +9183,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Bassano del grappa</t>
@@ -9238,10 +9222,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45847</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -9254,7 +9237,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Riese Pio X</t>
@@ -9265,7 +9247,11 @@
           <t>Fonte</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H163" t="n">
         <v>45.7292223</v>
       </c>
@@ -9290,10 +9276,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -9306,7 +9291,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Via Gregori 27</t>
@@ -9317,7 +9301,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H164" t="n">
         <v>45.500791</v>
       </c>
@@ -9342,10 +9330,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -9358,7 +9345,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Torreglia</t>
@@ -9369,7 +9355,11 @@
           <t>Torreglia</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H165" t="n">
         <v>45.3356668</v>
       </c>
@@ -9394,10 +9384,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -9410,7 +9399,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Mogliano Veneto</t>
@@ -9450,10 +9438,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -9466,7 +9453,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -9506,10 +9492,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -9522,7 +9507,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -9533,7 +9517,11 @@
           <t>Sovizzo</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H168" t="n">
         <v>45.5280283</v>
       </c>
@@ -9558,10 +9546,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -9574,7 +9561,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Barbarano Mossano</t>
@@ -9614,10 +9600,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -9630,7 +9615,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -9641,7 +9625,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H170" t="n">
         <v>45.6606078</v>
       </c>
@@ -9666,10 +9654,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -9682,7 +9669,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>Via Capitania 10</t>
@@ -9693,7 +9679,11 @@
           <t>Volpago del Montello</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H171" t="n">
         <v>45.7780578</v>
       </c>
@@ -9718,10 +9708,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -9734,7 +9723,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>San Pietro Mussolino</t>
@@ -9745,7 +9733,11 @@
           <t>San Pietro Mussolino</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H172" t="n">
         <v>45.5863045</v>
       </c>
@@ -9770,10 +9762,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -9786,7 +9777,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -9826,10 +9816,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -9842,7 +9831,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Mestrino</t>
@@ -9853,7 +9841,11 @@
           <t>Mestrino</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H174" t="n">
         <v>45.4427579</v>
       </c>
@@ -9878,10 +9870,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -9894,7 +9885,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -9934,10 +9924,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -9950,7 +9939,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Via Capitania 10</t>
@@ -9961,7 +9949,11 @@
           <t>Volpago del Montello</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H176" t="n">
         <v>45.7780578</v>
       </c>
@@ -9986,10 +9978,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45851</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -10002,7 +9993,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Sandrigo</t>
@@ -10013,7 +10003,11 @@
           <t>Sandrigo</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H177" t="n">
         <v>45.6606078</v>
       </c>
@@ -10038,10 +10032,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -10054,7 +10047,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -10094,10 +10086,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -10110,7 +10101,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Breda di Piave</t>
@@ -10121,7 +10111,11 @@
           <t>Breda di Piave</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H179" t="n">
         <v>45.7237273</v>
       </c>
@@ -10146,10 +10140,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -10162,7 +10155,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>Rovereto</t>
@@ -10173,7 +10165,11 @@
           <t>Rovereto</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
       <c r="H180" t="n">
         <v>45.886548</v>
       </c>
@@ -10198,10 +10194,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -10214,7 +10209,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -10254,10 +10248,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45853</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -10270,7 +10263,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Campo San Martino</t>
@@ -10281,7 +10273,11 @@
           <t>Campo San Martino</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H182" t="n">
         <v>45.544396</v>
       </c>
@@ -10306,10 +10302,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -10322,7 +10317,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -10362,10 +10356,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -10378,7 +10371,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Mussolente</t>
@@ -10389,7 +10381,11 @@
           <t>Mussolente</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H184" t="n">
         <v>45.7789522</v>
       </c>
@@ -10414,10 +10410,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -10430,7 +10425,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -10470,10 +10464,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -10486,7 +10479,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -10526,10 +10518,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -10542,7 +10533,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>Chiampo</t>
@@ -10553,7 +10543,11 @@
           <t>Chiampo</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H187" t="n">
         <v>45.5445732</v>
       </c>
@@ -10578,10 +10572,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -10594,7 +10587,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Vittorio Veneto</t>
@@ -10634,10 +10626,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -10650,7 +10641,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>San Donà di Piave</t>
@@ -10661,7 +10651,11 @@
           <t>San Donà di Piave</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H189" t="n">
         <v>45.6294811</v>
       </c>
@@ -10686,10 +10680,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -10702,7 +10695,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Padova</t>
@@ -10742,10 +10734,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -10758,7 +10749,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -10798,10 +10788,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -10814,7 +10803,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>Rubano</t>
@@ -10854,10 +10842,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -10870,7 +10857,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Via Grigno 16</t>
@@ -10910,10 +10896,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -10926,7 +10911,6 @@
           <t>Hypsugo Savii</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Via Lungo Giara 30/7</t>
@@ -10937,14 +10921,12 @@
           <t>San Tomio di Malo</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="n">
         <v>45.6392605</v>
       </c>
       <c r="I194" t="n">
         <v>11.4273472</v>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="n">
         <v>1</v>
       </c>
@@ -10958,10 +10940,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -10974,7 +10955,6 @@
           <t>Rhinolophus hipposideros</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>Via Borgo Masotto 8</t>
@@ -10985,7 +10965,11 @@
           <t>Cappella Maggiore</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="H195" t="n">
         <v>45.9878178</v>
       </c>
@@ -11005,11 +10989,9 @@
           <t>Colonia di oltre 300 individui in una mansarda (monitorata)</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -11022,7 +11004,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Corso SS. Felice e Fortunato 225</t>
@@ -11062,10 +11043,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -11078,7 +11058,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>Montemerlo</t>
@@ -11089,7 +11068,11 @@
           <t>Cervarese Santa Croce</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H197" t="n">
         <v>45.3771785</v>
       </c>
@@ -11114,10 +11097,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45885</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -11130,7 +11112,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>Cartigliano</t>
@@ -11141,7 +11122,11 @@
           <t>Cartigliano</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H198" t="n">
         <v>45.7130543</v>
       </c>
@@ -11166,10 +11151,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -11182,7 +11166,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Via Ludovico Ariosto</t>
@@ -11222,10 +11205,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -11238,7 +11220,6 @@
           <t>Eptesicus serotinus</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -11278,10 +11259,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -11294,7 +11274,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>Via Giorgio Dal Piaz</t>
@@ -11334,10 +11313,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45893</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -11350,7 +11328,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t xml:space="preserve">Piazza San Lorenzo </t>
@@ -11390,10 +11367,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45893</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -11406,7 +11382,6 @@
           <t>Eptesicus nilssonii</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Cornigian</t>
@@ -11417,7 +11392,11 @@
           <t>Val di Zoldo</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
       <c r="H203" t="n">
         <v>46.3664301</v>
       </c>
@@ -11442,10 +11421,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -11458,7 +11436,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>via Pagello 93</t>
@@ -11469,7 +11446,11 @@
           <t>Caldogno</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H204" t="n">
         <v>45.6170674</v>
       </c>
@@ -11494,10 +11475,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -11510,7 +11490,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -11550,10 +11529,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45899</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -11566,7 +11544,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>vicenza</t>
@@ -11606,10 +11583,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45899</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -11622,7 +11598,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Maserà di Padova</t>
@@ -11662,10 +11637,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -11678,7 +11652,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>Viale Sant'Agostino 565</t>
@@ -11718,10 +11691,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -11734,7 +11706,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Via Santa Lucia 4</t>
@@ -11774,10 +11745,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45907</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -11790,7 +11760,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>Contrà San Silvestro 61</t>
@@ -11830,10 +11799,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -11861,7 +11829,11 @@
           <t>Camisano Vicentino</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H211" t="n">
         <v>45.5142442</v>
       </c>
@@ -11886,10 +11858,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45909</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -11917,7 +11888,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H212" t="n">
         <v>45.5004723</v>
       </c>
@@ -11942,10 +11917,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -11958,7 +11932,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>Via Jacopo Crescini 9/4</t>
@@ -11998,10 +11971,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -12014,7 +11986,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -12025,7 +11996,11 @@
           <t>Longare</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H214" t="n">
         <v>45.4746344</v>
       </c>
@@ -12050,10 +12025,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45911</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -12066,7 +12040,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Via dei mille 187</t>
@@ -12106,10 +12079,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -12137,7 +12109,11 @@
           <t>Camisano Vicentino</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H216" t="n">
         <v>45.5220266</v>
       </c>
@@ -12162,10 +12138,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -12178,7 +12153,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -12218,10 +12192,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -12234,7 +12207,6 @@
           <t>Myotis sp.</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Via del commercio</t>
@@ -12274,10 +12246,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -12290,7 +12261,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Belluno</t>
@@ -12330,10 +12300,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -12346,7 +12315,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -12386,10 +12354,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -12402,7 +12369,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>Sossano</t>
@@ -12413,7 +12379,11 @@
           <t>Sossano</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H221" t="n">
         <v>45.358777</v>
       </c>
@@ -12438,10 +12408,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -12454,7 +12423,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>Sossano</t>
@@ -12465,7 +12433,11 @@
           <t>Sossano</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H222" t="n">
         <v>45.358777</v>
       </c>
@@ -12490,10 +12462,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -12506,7 +12477,6 @@
           <t>Vespertilio Murinus</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Via Monte delle rose, 62</t>
@@ -12517,7 +12487,11 @@
           <t>Arcugnano</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H223" t="n">
         <v>45.4944293</v>
       </c>
@@ -12542,10 +12516,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -12558,7 +12531,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -12598,10 +12570,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -12614,7 +12585,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -12654,10 +12624,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -12670,7 +12639,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Via Siracusa</t>
@@ -12710,10 +12678,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -12726,7 +12693,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Via IV novembre 29</t>
@@ -12737,7 +12703,11 @@
           <t>Eraclea</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H227" t="n">
         <v>45.5782995</v>
       </c>
@@ -12762,10 +12732,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -12778,7 +12747,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Via Giotto</t>
@@ -12818,10 +12786,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -12834,7 +12801,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Eraclea</t>
@@ -12845,7 +12811,11 @@
           <t>Eraclea</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
       <c r="H229" t="n">
         <v>45.5762676</v>
       </c>
@@ -12870,10 +12840,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -12886,7 +12855,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>via san marco 19</t>
@@ -12926,10 +12894,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -12942,7 +12909,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>Via Cesare Battisti 9/a</t>
@@ -12982,10 +12948,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -12998,7 +12963,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>Teolo</t>
@@ -13009,7 +12973,11 @@
           <t>Teolo</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
       <c r="H232" t="n">
         <v>45.365421</v>
       </c>
@@ -13034,10 +13002,9 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -13050,7 +13017,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>Costabissara</t>
@@ -13061,7 +13027,11 @@
           <t>Costabissara</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H233" t="n">
         <v>45.5855421</v>
       </c>
@@ -13086,10 +13056,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -13146,10 +13115,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -13206,10 +13174,9 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -13222,7 +13189,6 @@
           <t>Pipistrellus Kuhlii</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -13262,10 +13228,9 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -13278,7 +13243,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>Mogliano veneto</t>
@@ -13318,7 +13282,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/web/Pipistrelli 2025.xlsx
+++ b/web/Pipistrelli 2025.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Santorso </t>
+          <t>Santorso</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montecchio Maggiore</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Castegnero </t>
+          <t>Castegnero</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Isola Vicentina</t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Terrassa Padovana</t>
+          <t>Terrassa padovana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pojana Maggiore</t>
+          <t>Pojana maggiore</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pojana Maggiore</t>
+          <t>Pojana maggiore</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tezze sul Brenta</t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Campagna Lupia</t>
+          <t>Campagna lupia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Pietro in Gu</t>
+          <t>San pietro in gu</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martellago </t>
+          <t>Martellago</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martellago </t>
+          <t>Martellago</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villanova di Camposampiero</t>
+          <t>Villanova di camposampiero</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villanova di Camposampiero</t>
+          <t>Villanova di camposampiero</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Santa Maria Di Sala</t>
+          <t>Santa maria di sala</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cinto Euganeo</t>
+          <t>Cinto euganeo</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cinto Euganeo</t>
+          <t>Cinto euganeo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martino Di Lupari</t>
+          <t>San martino di lupari</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Vito di Leguzzano</t>
+          <t>San vito di leguzzano</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Galzignano Terme</t>
+          <t>Galzignano terme</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Boara Pisani</t>
+          <t>Boara pisani</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Villanova di Camposampiero</t>
+          <t>Villanova di camposampiero</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Carmignano di Brenta</t>
+          <t>Carmignano di brenta</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ponte San Nicolò</t>
+          <t>Ponte san nicolò</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ponte San Nicolò</t>
+          <t>Ponte san nicolò</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cavallino-Treporti</t>
+          <t>Cavallino-treporti</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Carmignano di Brenta</t>
+          <t>Carmignano di brenta</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>45.4641943</v>
+        <v>45.4408</v>
       </c>
       <c r="I136" t="n">
-        <v>9.1896346</v>
+        <v>12.3155</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fiesso d'Artico</t>
+          <t>Fiesso d'artico</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Recoaro Terme</t>
+          <t>Recoaro terme</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>45.9662071</v>
+        <v>45.4408</v>
       </c>
       <c r="I152" t="n">
-        <v>12.6945529</v>
+        <v>12.3155</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bolzano Vicentino</t>
+          <t>Bolzano vicentino</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lozzo Atestino</t>
+          <t>Lozzo atestino</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Selvazzano Dentro</t>
+          <t>Selvazzano dentro</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Piazzola sul Brenta</t>
+          <t>Piazzola sul brenta</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mogliano Veneto</t>
+          <t>Mogliano veneto</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barbarano Mossano</t>
+          <t>Barbarano mossano</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Volpago del Montello</t>
+          <t>Volpago del montello</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>San Pietro Mussolino</t>
+          <t>San pietro mussolino</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Volpago del Montello</t>
+          <t>Volpago del montello</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Breda di Piave</t>
+          <t>Breda di piave</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Campo San Martino</t>
+          <t>Campo san martino</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vittorio Veneto</t>
+          <t>Vittorio veneto</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San Donà di Piave</t>
+          <t>San donà di piave</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Cappella Maggiore</t>
+          <t>Cappella maggiore</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cervarese Santa Croce</t>
+          <t>Cervarese santa croce</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Val di Zoldo</t>
+          <t>Val di zoldo</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Maserà di Padova</t>
+          <t>Maserà di padova</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">

--- a/web/Pipistrelli 2025.xlsx
+++ b/web/Pipistrelli 2025.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Terrassa padovana</t>
+          <t>Terrassa Padovana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pojana maggiore</t>
+          <t>Pojana Maggiore</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pojana maggiore</t>
+          <t>Pojana Maggiore</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Campagna lupia</t>
+          <t>Campagna Lupia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San pietro in gu</t>
+          <t>San Pietro In Gu</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Villanova di camposampiero</t>
+          <t>Villanova Di Camposampiero</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Villanova di camposampiero</t>
+          <t>Villanova Di Camposampiero</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Santa maria di sala</t>
+          <t>Santa Maria Di Sala</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cinto euganeo</t>
+          <t>Cinto Euganeo</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cinto euganeo</t>
+          <t>Cinto Euganeo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San martino di lupari</t>
+          <t>San Martino Di Lupari</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San vito di leguzzano</t>
+          <t>San Vito Di Leguzzano</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Marano vicentino</t>
+          <t>Marano Vicentino</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Marano vicentino</t>
+          <t>Marano Vicentino</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Marano vicentino</t>
+          <t>Marano Vicentino</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Galzignano terme</t>
+          <t>Galzignano Terme</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Boara pisani</t>
+          <t>Boara Pisani</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Villanova di camposampiero</t>
+          <t>Villanova Di Camposampiero</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Carmignano di brenta</t>
+          <t>Carmignano Di Brenta</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ponte san nicolò</t>
+          <t>Ponte San Nicolò</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ponte san nicolò</t>
+          <t>Ponte San Nicolò</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cavallino-treporti</t>
+          <t>Cavallino-Treporti</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Carmignano di brenta</t>
+          <t>Carmignano Di Brenta</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fiesso d'artico</t>
+          <t>Fiesso D'Artico</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Recoaro terme</t>
+          <t>Recoaro Terme</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bolzano vicentino</t>
+          <t>Bolzano Vicentino</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lozzo atestino</t>
+          <t>Lozzo Atestino</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Selvazzano dentro</t>
+          <t>Selvazzano Dentro</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Piazzola sul brenta</t>
+          <t>Piazzola Sul Brenta</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mogliano veneto</t>
+          <t>Mogliano Veneto</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barbarano mossano</t>
+          <t>Barbarano Mossano</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Volpago del montello</t>
+          <t>Volpago Del Montello</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>San pietro mussolino</t>
+          <t>San Pietro Mussolino</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Volpago del montello</t>
+          <t>Volpago Del Montello</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Breda di piave</t>
+          <t>Breda Di Piave</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Campo san martino</t>
+          <t>Campo San Martino</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vittorio veneto</t>
+          <t>Vittorio Veneto</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>San donà di piave</t>
+          <t>San Donà Di Piave</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Cappella maggiore</t>
+          <t>Cappella Maggiore</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cervarese santa croce</t>
+          <t>Cervarese Santa Croce</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Val di zoldo</t>
+          <t>Val Di Zoldo</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Maserà di padova</t>
+          <t>Maserà Di Padova</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mogliano veneto</t>
+          <t>Mogliano Veneto</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">

--- a/web/Pipistrelli 2025.xlsx
+++ b/web/Pipistrelli 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcello\AndroidStudioProjects\BatMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD175EA-90B8-45C6-8895-5F506AF9E252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B527845-1F6D-43E2-B5C3-9F9E93EF5703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4785" yWindow="2655" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1852,9 +1852,6 @@
     <t>Nyctalus noctula</t>
   </si>
   <si>
-    <t>Via San Marco</t>
-  </si>
-  <si>
     <t>Debilitato, nel vano scala di un palazzo storico, presenti un centinaio di trombiculidi</t>
   </si>
   <si>
@@ -1877,6 +1874,9 @@
   </si>
   <si>
     <t>Castelgomberto</t>
+  </si>
+  <si>
+    <t>Via San Marco 105</t>
   </si>
 </sst>
 </file>
@@ -5901,7 +5901,7 @@
         <v>267</v>
       </c>
       <c r="F96" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G96" t="s">
         <v>19</v>
@@ -6775,7 +6775,7 @@
         <v>324</v>
       </c>
       <c r="F119" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G119" t="s">
         <v>19</v>
@@ -11145,7 +11145,7 @@
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F234" t="s">
         <v>62</v>
@@ -11166,7 +11166,7 @@
         <v>1</v>
       </c>
       <c r="L234" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="M234" t="s">
         <v>42</v>
@@ -11186,7 +11186,7 @@
         <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F235" t="s">
         <v>62</v>
@@ -11207,7 +11207,7 @@
         <v>1</v>
       </c>
       <c r="L235" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M235" t="s">
         <v>54</v>
@@ -11218,10 +11218,10 @@
         <v>46019</v>
       </c>
       <c r="B236" t="s">
+        <v>612</v>
+      </c>
+      <c r="C236" t="s">
         <v>613</v>
-      </c>
-      <c r="C236" t="s">
-        <v>614</v>
       </c>
       <c r="E236" t="s">
         <v>66</v>
@@ -11256,13 +11256,13 @@
         <v>46020</v>
       </c>
       <c r="B237" t="s">
+        <v>614</v>
+      </c>
+      <c r="C237" t="s">
+        <v>35</v>
+      </c>
+      <c r="E237" t="s">
         <v>615</v>
-      </c>
-      <c r="C237" t="s">
-        <v>35</v>
-      </c>
-      <c r="E237" t="s">
-        <v>616</v>
       </c>
       <c r="F237" t="s">
         <v>434</v>
@@ -11283,7 +11283,7 @@
         <v>1</v>
       </c>
       <c r="L237" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M237" t="s">
         <v>54</v>
